--- a/docs/marketing/direct_712841876_filled.xlsx
+++ b/docs/marketing/direct_712841876_filled.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="BD12" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE12" s="9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="BD13" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE13" s="9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BD14" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE14" s="9" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="BD15" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE15" s="9" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="BD16" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE16" s="9" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="BD17" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE17" s="9" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="BD18" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE18" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BD19" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE19" s="9" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="BD20" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE20" s="9" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="BD21" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE21" s="9" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="BD22" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE22" s="9" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="BD23" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE23" s="9" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="BD24" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE24" s="9" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="BD25" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE25" s="9" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="BD26" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE26" s="9" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="BD27" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE27" s="9" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BD28" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE28" s="9" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BD29" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE29" s="9" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BD30" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE30" s="9" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="BD31" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE31" s="9" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="BD32" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE32" s="9" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="BD33" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE33" s="9" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="BD34" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE34" s="9" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BD35" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE35" s="9" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="BD36" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE36" s="9" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="BD37" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE37" s="9" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="BD38" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE38" s="9" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="BD39" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE39" s="9" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="BD40" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE40" s="9" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="BD41" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE41" s="9" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="BD42" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE42" s="9" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="BD43" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE43" s="9" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BD44" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE44" s="9" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="BD45" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE45" s="9" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="BD46" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE46" s="9" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="BD47" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE47" s="9" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="BD48" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE48" s="9" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="BD49" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE49" s="9" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="BD50" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE50" s="9" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BD51" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE51" s="9" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="BD52" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE52" s="9" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="BD53" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE53" s="9" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="BD54" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE54" s="9" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BD55" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE55" s="9" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="BD56" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE56" s="9" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="BD57" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE57" s="9" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BD58" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE58" s="9" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="BD59" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE59" s="9" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="BD60" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE60" s="9" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BD61" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE61" s="9" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="BD62" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE62" s="9" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="BD63" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE63" s="9" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="BD64" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE64" s="9" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="BD65" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE65" s="9" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="BD66" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE66" s="9" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="BD67" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE67" s="9" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="BD68" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE68" s="9" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="BD69" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE69" s="9" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="BD70" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE70" s="9" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="BD71" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE71" s="9" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="BD72" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE72" s="9" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="BD73" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE73" s="9" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="BD74" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE74" s="9" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="BD75" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE75" s="9" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="BD76" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE76" s="9" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="BD77" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE77" s="9" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="BD78" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE78" s="9" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="BD79" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE79" s="9" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="BD80" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE80" s="9" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="BD81" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE81" s="9" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="BD82" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE82" s="9" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="BD83" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE83" s="9" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="BD84" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE84" s="9" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="BD85" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE85" s="9" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="BD86" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE86" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="BD87" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE87" s="9" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="BD88" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE88" s="9" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="BD89" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE89" s="9" t="inlineStr">

--- a/docs/marketing/direct_712841876_filled.xlsx
+++ b/docs/marketing/direct_712841876_filled.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="BD12" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE12" s="9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="BD13" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE13" s="9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BD14" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE14" s="9" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="BD15" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE15" s="9" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="BD16" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE16" s="9" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="BD17" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE17" s="9" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="BD18" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE18" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BD19" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE19" s="9" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="BD20" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE20" s="9" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="BD21" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE21" s="9" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="BD22" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE22" s="9" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="BD23" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE23" s="9" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="BD24" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE24" s="9" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="BD25" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE25" s="9" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="BD26" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE26" s="9" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="BD27" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE27" s="9" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BD28" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE28" s="9" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BD29" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE29" s="9" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BD30" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE30" s="9" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="BD31" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE31" s="9" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="BD32" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE32" s="9" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="BD33" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE33" s="9" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="BD34" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE34" s="9" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BD35" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE35" s="9" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="BD36" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE36" s="9" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="BD37" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE37" s="9" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="BD38" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE38" s="9" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="BD39" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE39" s="9" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="BD40" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE40" s="9" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="BD41" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE41" s="9" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="BD42" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE42" s="9" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="BD43" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE43" s="9" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BD44" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE44" s="9" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="BD45" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE45" s="9" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="BD46" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE46" s="9" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="BD47" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE47" s="9" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="BD48" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE48" s="9" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="BD49" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE49" s="9" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="BD50" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE50" s="9" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BD51" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE51" s="9" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="BD52" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE52" s="9" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="BD53" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE53" s="9" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="BD54" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE54" s="9" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BD55" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE55" s="9" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="BD56" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE56" s="9" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="BD57" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE57" s="9" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BD58" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE58" s="9" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="BD59" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE59" s="9" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="BD60" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE60" s="9" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BD61" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE61" s="9" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="BD62" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE62" s="9" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="BD63" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE63" s="9" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="BD64" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE64" s="9" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="BD65" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE65" s="9" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="BD66" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE66" s="9" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="BD67" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE67" s="9" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="BD68" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE68" s="9" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="BD69" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE69" s="9" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="BD70" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE70" s="9" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="BD71" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE71" s="9" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="BD72" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE72" s="9" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="BD73" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE73" s="9" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="BD74" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE74" s="9" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="BD75" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE75" s="9" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="BD76" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE76" s="9" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="BD77" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE77" s="9" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="BD78" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE78" s="9" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="BD79" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE79" s="9" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="BD80" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE80" s="9" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="BD81" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE81" s="9" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="BD82" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE82" s="9" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="BD83" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE83" s="9" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="BD84" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE84" s="9" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="BD85" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE85" s="9" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="BD86" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE86" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="BD87" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE87" s="9" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="BD88" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE88" s="9" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="BD89" s="9" t="inlineStr">
         <is>
-          <t>Настроим под вашу задачу за 1 день||Файл → настройка → приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
+          <t>Настроим под вашу задачу за 1 день||Файл, настройка, готовое приложение||10 готовых решений по задачам||Статьи и разборы по автоматизации</t>
         </is>
       </c>
       <c r="BE89" s="9" t="inlineStr">

--- a/docs/marketing/direct_712841876_filled.xlsx
+++ b/docs/marketing/direct_712841876_filled.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A6:BN89"/>
+  <dimension ref="A1:BN89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="10" min="1" max="8"/>
@@ -615,6 +615,11 @@
     <col width="12.7109375" customWidth="1" style="10" min="61" max="66"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="20.1" customHeight="1" s="10">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -2464,7 +2469,7 @@
       <c r="U19" s="9" t="inlineStr"/>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>Сопоставим 20 000 позиций за 3 часа. Отчеты, дашборды, роли. Демо за 1 день.</t>
+          <t>Сопоставим 22 000 позиций за 3 часа. Отчеты, дашборды, роли. Демо за 1 день.</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr"/>
@@ -15654,7 +15659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.7109375" customWidth="1" style="10" min="1" max="1"/>
@@ -15662,6 +15667,7 @@
     <col width="8.7109375" customWidth="1" style="10" min="3" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -15690,6 +15696,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>

--- a/docs/marketing/direct_712841876_filled.xlsx
+++ b/docs/marketing/direct_712841876_filled.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN89"/>
+  <dimension ref="A6:BN89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="10" min="1" max="8"/>
@@ -615,11 +615,6 @@
     <col width="12.7109375" customWidth="1" style="10" min="61" max="66"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="20.1" customHeight="1" s="10">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1239,7 +1234,7 @@
       </c>
       <c r="BC12" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD12" s="9" t="inlineStr">
@@ -1432,7 +1427,7 @@
       </c>
       <c r="BC13" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD13" s="9" t="inlineStr">
@@ -1625,7 +1620,7 @@
       </c>
       <c r="BC14" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD14" s="9" t="inlineStr">
@@ -1818,7 +1813,7 @@
       </c>
       <c r="BC15" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD15" s="9" t="inlineStr">
@@ -2011,7 +2006,7 @@
       </c>
       <c r="BC16" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD16" s="9" t="inlineStr">
@@ -2202,7 +2197,7 @@
       </c>
       <c r="BC17" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD17" s="9" t="inlineStr">
@@ -2377,7 +2372,7 @@
       <c r="BB18" s="9" t="inlineStr"/>
       <c r="BC18" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD18" s="9" t="inlineStr">
@@ -2548,7 +2543,7 @@
       <c r="BB19" s="9" t="inlineStr"/>
       <c r="BC19" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD19" s="9" t="inlineStr">
@@ -2737,7 +2732,7 @@
       </c>
       <c r="BC20" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD20" s="9" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="BC21" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD21" s="9" t="inlineStr">
@@ -3123,7 +3118,7 @@
       </c>
       <c r="BC22" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD22" s="9" t="inlineStr">
@@ -3316,7 +3311,7 @@
       </c>
       <c r="BC23" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD23" s="9" t="inlineStr">
@@ -3507,7 +3502,7 @@
       </c>
       <c r="BC24" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD24" s="9" t="inlineStr">
@@ -3682,7 +3677,7 @@
       <c r="BB25" s="9" t="inlineStr"/>
       <c r="BC25" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD25" s="9" t="inlineStr">
@@ -3853,7 +3848,7 @@
       <c r="BB26" s="9" t="inlineStr"/>
       <c r="BC26" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD26" s="9" t="inlineStr">
@@ -4042,7 +4037,7 @@
       </c>
       <c r="BC27" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD27" s="9" t="inlineStr">
@@ -4235,7 +4230,7 @@
       </c>
       <c r="BC28" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD28" s="9" t="inlineStr">
@@ -4428,7 +4423,7 @@
       </c>
       <c r="BC29" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD29" s="9" t="inlineStr">
@@ -4621,7 +4616,7 @@
       </c>
       <c r="BC30" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD30" s="9" t="inlineStr">
@@ -4812,7 +4807,7 @@
       </c>
       <c r="BC31" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD31" s="9" t="inlineStr">
@@ -4987,7 +4982,7 @@
       <c r="BB32" s="9" t="inlineStr"/>
       <c r="BC32" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD32" s="9" t="inlineStr">
@@ -5158,7 +5153,7 @@
       <c r="BB33" s="9" t="inlineStr"/>
       <c r="BC33" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD33" s="9" t="inlineStr">
@@ -5347,7 +5342,7 @@
       </c>
       <c r="BC34" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD34" s="9" t="inlineStr">
@@ -5540,7 +5535,7 @@
       </c>
       <c r="BC35" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD35" s="9" t="inlineStr">
@@ -5733,7 +5728,7 @@
       </c>
       <c r="BC36" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD36" s="9" t="inlineStr">
@@ -5926,7 +5921,7 @@
       </c>
       <c r="BC37" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD37" s="9" t="inlineStr">
@@ -6117,7 +6112,7 @@
       </c>
       <c r="BC38" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD38" s="9" t="inlineStr">
@@ -6292,7 +6287,7 @@
       <c r="BB39" s="9" t="inlineStr"/>
       <c r="BC39" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD39" s="9" t="inlineStr">
@@ -6463,7 +6458,7 @@
       <c r="BB40" s="9" t="inlineStr"/>
       <c r="BC40" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD40" s="9" t="inlineStr">
@@ -6652,7 +6647,7 @@
       </c>
       <c r="BC41" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD41" s="9" t="inlineStr">
@@ -6845,7 +6840,7 @@
       </c>
       <c r="BC42" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD42" s="9" t="inlineStr">
@@ -7038,7 +7033,7 @@
       </c>
       <c r="BC43" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD43" s="9" t="inlineStr">
@@ -7231,7 +7226,7 @@
       </c>
       <c r="BC44" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD44" s="9" t="inlineStr">
@@ -7422,7 +7417,7 @@
       </c>
       <c r="BC45" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD45" s="9" t="inlineStr">
@@ -7597,7 +7592,7 @@
       <c r="BB46" s="9" t="inlineStr"/>
       <c r="BC46" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD46" s="9" t="inlineStr">
@@ -7768,7 +7763,7 @@
       <c r="BB47" s="9" t="inlineStr"/>
       <c r="BC47" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD47" s="9" t="inlineStr">
@@ -7957,7 +7952,7 @@
       </c>
       <c r="BC48" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD48" s="9" t="inlineStr">
@@ -8150,7 +8145,7 @@
       </c>
       <c r="BC49" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD49" s="9" t="inlineStr">
@@ -8343,7 +8338,7 @@
       </c>
       <c r="BC50" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD50" s="9" t="inlineStr">
@@ -8536,7 +8531,7 @@
       </c>
       <c r="BC51" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD51" s="9" t="inlineStr">
@@ -8727,7 +8722,7 @@
       </c>
       <c r="BC52" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD52" s="9" t="inlineStr">
@@ -8902,7 +8897,7 @@
       <c r="BB53" s="9" t="inlineStr"/>
       <c r="BC53" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD53" s="9" t="inlineStr">
@@ -9073,7 +9068,7 @@
       <c r="BB54" s="9" t="inlineStr"/>
       <c r="BC54" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD54" s="9" t="inlineStr">
@@ -9262,7 +9257,7 @@
       </c>
       <c r="BC55" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD55" s="9" t="inlineStr">
@@ -9455,7 +9450,7 @@
       </c>
       <c r="BC56" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD56" s="9" t="inlineStr">
@@ -9648,7 +9643,7 @@
       </c>
       <c r="BC57" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD57" s="9" t="inlineStr">
@@ -9841,7 +9836,7 @@
       </c>
       <c r="BC58" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD58" s="9" t="inlineStr">
@@ -10032,7 +10027,7 @@
       </c>
       <c r="BC59" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD59" s="9" t="inlineStr">
@@ -10207,7 +10202,7 @@
       <c r="BB60" s="9" t="inlineStr"/>
       <c r="BC60" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD60" s="9" t="inlineStr">
@@ -10378,7 +10373,7 @@
       <c r="BB61" s="9" t="inlineStr"/>
       <c r="BC61" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD61" s="9" t="inlineStr">
@@ -10567,7 +10562,7 @@
       </c>
       <c r="BC62" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD62" s="9" t="inlineStr">
@@ -10760,7 +10755,7 @@
       </c>
       <c r="BC63" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD63" s="9" t="inlineStr">
@@ -10953,7 +10948,7 @@
       </c>
       <c r="BC64" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD64" s="9" t="inlineStr">
@@ -11146,7 +11141,7 @@
       </c>
       <c r="BC65" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD65" s="9" t="inlineStr">
@@ -11337,7 +11332,7 @@
       </c>
       <c r="BC66" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD66" s="9" t="inlineStr">
@@ -11512,7 +11507,7 @@
       <c r="BB67" s="9" t="inlineStr"/>
       <c r="BC67" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD67" s="9" t="inlineStr">
@@ -11683,7 +11678,7 @@
       <c r="BB68" s="9" t="inlineStr"/>
       <c r="BC68" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD68" s="9" t="inlineStr">
@@ -11872,7 +11867,7 @@
       </c>
       <c r="BC69" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD69" s="9" t="inlineStr">
@@ -12065,7 +12060,7 @@
       </c>
       <c r="BC70" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD70" s="9" t="inlineStr">
@@ -12258,7 +12253,7 @@
       </c>
       <c r="BC71" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD71" s="9" t="inlineStr">
@@ -12451,7 +12446,7 @@
       </c>
       <c r="BC72" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD72" s="9" t="inlineStr">
@@ -12642,7 +12637,7 @@
       </c>
       <c r="BC73" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD73" s="9" t="inlineStr">
@@ -12817,7 +12812,7 @@
       <c r="BB74" s="9" t="inlineStr"/>
       <c r="BC74" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD74" s="9" t="inlineStr">
@@ -12984,7 +12979,7 @@
       <c r="BB75" s="9" t="inlineStr"/>
       <c r="BC75" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD75" s="9" t="inlineStr">
@@ -13169,7 +13164,7 @@
       </c>
       <c r="BC76" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD76" s="9" t="inlineStr">
@@ -13362,7 +13357,7 @@
       </c>
       <c r="BC77" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD77" s="9" t="inlineStr">
@@ -13555,7 +13550,7 @@
       </c>
       <c r="BC78" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD78" s="9" t="inlineStr">
@@ -13748,7 +13743,7 @@
       </c>
       <c r="BC79" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD79" s="9" t="inlineStr">
@@ -13939,7 +13934,7 @@
       </c>
       <c r="BC80" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD80" s="9" t="inlineStr">
@@ -14110,7 +14105,7 @@
       <c r="BB81" s="9" t="inlineStr"/>
       <c r="BC81" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD81" s="9" t="inlineStr">
@@ -14277,7 +14272,7 @@
       <c r="BB82" s="9" t="inlineStr"/>
       <c r="BC82" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD82" s="9" t="inlineStr">
@@ -14466,7 +14461,7 @@
       </c>
       <c r="BC83" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD83" s="9" t="inlineStr">
@@ -14659,7 +14654,7 @@
       </c>
       <c r="BC84" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD84" s="9" t="inlineStr">
@@ -14852,7 +14847,7 @@
       </c>
       <c r="BC85" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD85" s="9" t="inlineStr">
@@ -15045,7 +15040,7 @@
       </c>
       <c r="BC86" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD86" s="9" t="inlineStr">
@@ -15236,7 +15231,7 @@
       </c>
       <c r="BC87" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD87" s="9" t="inlineStr">
@@ -15411,7 +15406,7 @@
       <c r="BB88" s="9" t="inlineStr"/>
       <c r="BC88" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD88" s="9" t="inlineStr">
@@ -15582,7 +15577,7 @@
       <c r="BB89" s="9" t="inlineStr"/>
       <c r="BC89" s="9" t="inlineStr">
         <is>
-          <t>Заказать демо||Как это работает||Все решения вместо Excel||База знаний</t>
+          <t>Заказать демо||Как это работает||Готовые решения||База знаний</t>
         </is>
       </c>
       <c r="BD89" s="9" t="inlineStr">
@@ -15659,7 +15654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="B2:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.7109375" customWidth="1" style="10" min="1" max="1"/>
@@ -15667,7 +15662,6 @@
     <col width="8.7109375" customWidth="1" style="10" min="3" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -15696,7 +15690,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
